--- a/data/trans_dic/P21B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P21B_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>81,07%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>85,41; 97,55</t>
+          <t>84,56; 97,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,95; 100,0</t>
+          <t>88,63; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>79,3; 95,67</t>
+          <t>79,86; 95,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>73,18; 86,99</t>
+          <t>73,58; 87,38</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>86,37; 98,63</t>
+          <t>85,26; 98,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,21; 91,37</t>
+          <t>73,59; 90,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,25; 85,15</t>
+          <t>63,22; 84,94</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>77,08; 89,69</t>
+          <t>78,16; 89,94</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>88,66; 96,98</t>
+          <t>88,69; 96,85</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>82,02; 93,38</t>
+          <t>82,45; 93,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>74,57; 88,37</t>
+          <t>74,9; 87,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,65; 86,66</t>
+          <t>78,07; 87,24</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>83,66%</t>
+          <t>83,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,95%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,99; 95,72</t>
+          <t>76,67; 95,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77,84; 95,49</t>
+          <t>78,31; 94,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>66,88; 89,97</t>
+          <t>66,66; 90,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,68; 91,08</t>
+          <t>75,07; 91,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>84,98; 97,7</t>
+          <t>84,84; 97,47</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>91,3; 98,98</t>
+          <t>91,77; 100,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>74,97; 91,97</t>
+          <t>76,81; 92,51</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>77,0; 88,66</t>
+          <t>77,26; 89,06</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>84,85; 95,28</t>
+          <t>84,41; 95,4</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>88,1; 96,85</t>
+          <t>86,91; 96,28</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75,76; 89,82</t>
+          <t>76,48; 89,64</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>78,4; 88,33</t>
+          <t>78,13; 88,37</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>92,06; 100,0</t>
+          <t>93,56; 100,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>95,93; 100,0</t>
+          <t>95,8; 100,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>85,23; 98,5</t>
+          <t>87,11; 97,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,33; 97,26</t>
+          <t>86,24; 97,29</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>82,83; 98,1</t>
+          <t>82,78; 98,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>85,03; 100,0</t>
+          <t>86,87; 100,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>73,24; 96,98</t>
+          <t>73,19; 96,89</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>88,5; 97,74</t>
+          <t>87,46; 97,77</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>92,38; 98,75</t>
+          <t>92,59; 98,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95,44; 99,54</t>
+          <t>95,67; 99,54</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>86,79; 97,01</t>
+          <t>87,01; 96,96</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>88,1; 96,68</t>
+          <t>88,66; 96,81</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,28%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,56; 99,07</t>
+          <t>94,69; 98,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96,78; 100,0</t>
+          <t>96,82; 100,0</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>91,77; 98,11</t>
+          <t>91,37; 98,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>92,31; 98,37</t>
+          <t>92,66; 98,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,96; 98,95</t>
+          <t>93,94; 98,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,32; 99,16</t>
+          <t>93,28; 99,18</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,38; 97,22</t>
+          <t>89,94; 97,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>93,04; 99,36</t>
+          <t>90,45; 96,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,34; 98,64</t>
+          <t>95,29; 98,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>96,02; 99,21</t>
+          <t>96,15; 99,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>91,91; 96,96</t>
+          <t>92,27; 97,06</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,51; 99,06</t>
+          <t>92,91; 96,98</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>94,5%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>79,15; 98,14</t>
+          <t>77,71; 98,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>95,07; 100,0</t>
+          <t>93,65; 100,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>90,54; 98,95</t>
+          <t>90,33; 98,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>78,15; 98,03</t>
+          <t>79,63; 97,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>95,97; 100,0</t>
+          <t>95,77; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>96,51; 99,58</t>
+          <t>96,5; 99,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>94,77; 99,38</t>
+          <t>94,78; 99,38</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>92,92; 97,97</t>
+          <t>92,25; 97,7</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>91,97; 98,64</t>
+          <t>92,86; 98,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96,84; 99,42</t>
+          <t>96,73; 99,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94,45; 98,79</t>
+          <t>94,7; 98,74</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>90,51; 97,29</t>
+          <t>90,32; 96,77</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,26%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>90,1; 100,0</t>
+          <t>88,14; 100,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>90,34; 100,0</t>
+          <t>91,65; 100,0</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>81,44; 96,68</t>
+          <t>80,47; 96,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>95,71; 99,27</t>
+          <t>95,64; 99,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96,67; 99,67</t>
+          <t>96,99; 99,65</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>92,4; 98,66</t>
+          <t>92,31; 98,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>88,45; 96,3</t>
+          <t>87,53; 96,21</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>95,83; 99,07</t>
+          <t>95,79; 99,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>97,0; 99,47</t>
+          <t>96,97; 99,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91,51; 97,27</t>
+          <t>91,47; 97,21</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>90,69; 97,37</t>
+          <t>89,88; 97,09</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>91,61%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>93,33; 96,91</t>
+          <t>93,1; 96,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>95,94; 98,49</t>
+          <t>95,81; 98,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>90,09; 94,58</t>
+          <t>90,25; 94,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88,73; 93,42</t>
+          <t>88,79; 93,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,29; 97,81</t>
+          <t>95,36; 97,81</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,65; 98,01</t>
+          <t>95,46; 97,88</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,33; 94,61</t>
+          <t>90,08; 94,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90,95; 96,39</t>
+          <t>90,13; 93,36</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>95,04; 97,16</t>
+          <t>95,08; 97,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>96,13; 97,89</t>
+          <t>96,13; 97,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>91,07; 94,09</t>
+          <t>91,18; 94,18</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>90,95; 95,04</t>
+          <t>90,17; 92,85</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98056</t>
+          <t>105999</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>91815</t>
+          <t>100197</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>189870</t>
+          <t>206196</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66752; 76246</t>
+          <t>66091; 76284</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46116; 53040</t>
+          <t>47010; 53040</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50943; 61457</t>
+          <t>51301; 61299</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>88867; 105636</t>
+          <t>96202; 114248</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>59207; 67613</t>
+          <t>58448; 67341</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58557; 73080</t>
+          <t>58862; 72667</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48986; 63927</t>
+          <t>47467; 63773</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>84067; 97825</t>
+          <t>92201; 106092</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>130075; 142282</t>
+          <t>130125; 142095</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>109110; 124213</t>
+          <t>109675; 124960</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>103882; 123108</t>
+          <t>104351; 122286</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>176671; 199763</t>
+          <t>194161; 216972</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>65609</t>
+          <t>69567</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>82654</t>
+          <t>91096</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>148265</t>
+          <t>160664</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>50657; 62175</t>
+          <t>49798; 62204</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>55428; 67997</t>
+          <t>55766; 67359</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>34843; 46870</t>
+          <t>34728; 47062</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57899; 70620</t>
+          <t>61726; 75314</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>77516; 89122</t>
+          <t>77395; 88916</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79113; 85768</t>
+          <t>79525; 86654</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60917; 74733</t>
+          <t>62416; 75173</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>76071; 87594</t>
+          <t>84338; 97215</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>132516; 148812</t>
+          <t>131835; 148999</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>139075; 152883</t>
+          <t>137194; 151987</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>101035; 119782</t>
+          <t>101987; 119539</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>138250; 155754</t>
+          <t>149520; 169125</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>90244</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>49169</t>
+          <t>55429</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>130288</t>
+          <t>145673</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88746; 96404</t>
+          <t>90197; 96404</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>149735; 156095</t>
+          <t>149544; 156095</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75295; 87024</t>
+          <t>76961; 86463</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>74697; 85136</t>
+          <t>83416; 94104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>38699; 45831</t>
+          <t>38673; 45832</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45402; 53396</t>
+          <t>46387; 53396</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>22807; 30200</t>
+          <t>22794; 30173</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>46267; 51094</t>
+          <t>51453; 57521</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>132214; 141332</t>
+          <t>132517; 141293</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>199937; 208532</t>
+          <t>200428; 208537</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>103703; 115920</t>
+          <t>103963; 115855</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>123175; 135179</t>
+          <t>137922; 150595</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217847</t>
+          <t>240504</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>409770</t>
+          <t>231464</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>627618</t>
+          <t>471967</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>212783; 222937</t>
+          <t>213090; 222312</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>246443; 254649</t>
+          <t>246562; 254649</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>171080; 182903</t>
+          <t>170330; 183312</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>208557; 222235</t>
+          <t>231446; 245768</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>177071; 186478</t>
+          <t>177022; 186523</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>206987; 219947</t>
+          <t>206908; 220002</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>178838; 192370</t>
+          <t>177978; 192360</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>393134; 419817</t>
+          <t>221883; 237150</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>394195; 407839</t>
+          <t>393989; 407139</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>457507; 472719</t>
+          <t>458128; 472990</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>353220; 372617</t>
+          <t>354600; 373013</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>612827; 642354</t>
+          <t>459987; 480137</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90066</t>
+          <t>101116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>169948</t>
+          <t>190508</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>260014</t>
+          <t>291624</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>38845; 48161</t>
+          <t>38136; 48138</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>103587; 108960</t>
+          <t>102040; 108960</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>88793; 97041</t>
+          <t>88592; 97005</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>75454; 94641</t>
+          <t>87074; 106817</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>131915; 137459</t>
+          <t>131647; 137459</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>223691; 230799</t>
+          <t>223658; 230792</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>140911; 147769</t>
+          <t>140920; 147762</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>164661; 173617</t>
+          <t>183808; 194657</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>171550; 183996</t>
+          <t>173206; 183937</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>329980; 338751</t>
+          <t>329588; 338762</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>233060; 243779</t>
+          <t>233688; 243663</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>247772; 266339</t>
+          <t>278717; 298619</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>150294</t>
+          <t>162715</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>196357</t>
+          <t>205092</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40385; 44824</t>
+          <t>39509; 44824</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>53036; 58710</t>
+          <t>53808; 58710</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>50726; 60220</t>
+          <t>50124; 60131</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>279105; 289470</t>
+          <t>278891; 289234</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>291533; 300573</t>
+          <t>292479; 300511</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>198914; 212370</t>
+          <t>198716; 212115</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>142315; 154947</t>
+          <t>153359; 168569</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>322410; 333319</t>
+          <t>322265; 333406</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>349473; 358360</t>
+          <t>349375; 358349</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>253991; 269977</t>
+          <t>253863; 269812</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>187686; 201511</t>
+          <t>195574; 211259</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>598759</t>
+          <t>649808</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>953650</t>
+          <t>831409</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1552411</t>
+          <t>1481216</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>521171; 541164</t>
+          <t>519926; 541582</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>674107; 692031</t>
+          <t>673217; 691697</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>496819; 521563</t>
+          <t>497676; 522076</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>581196; 611945</t>
+          <t>631481; 664330</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>785172; 805944</t>
+          <t>785811; 805989</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>932792; 955745</t>
+          <t>930893; 954558</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>676864; 708890</t>
+          <t>674988; 708250</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>928419; 983890</t>
+          <t>816320; 845592</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1313868; 1343182</t>
+          <t>1314420; 1343697</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1612921; 1642523</t>
+          <t>1612846; 1642696</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1184632; 1223872</t>
+          <t>1186026; 1225070</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1524088; 1592734</t>
+          <t>1458002; 1501239</t>
         </is>
       </c>
     </row>
